--- a/01_Thermal/B_results/Four_Fan_Annular_GP/four_annular_gp_summary.xlsx
+++ b/01_Thermal/B_results/Four_Fan_Annular_GP/four_annular_gp_summary.xlsx
@@ -526,29 +526,29 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1739640830539662</v>
+        <v>0.1976400252378546</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2919092932826493</v>
+        <v>0.3245574595747438</v>
       </c>
       <c r="D2" t="n">
-        <v>237.4609733686638</v>
+        <v>269.7786344496716</v>
       </c>
       <c r="E2" t="n">
-        <v>116.3130634640189</v>
+        <v>143.7857483320596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2284866245261445</v>
+        <v>0.2638759599380512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9061869025268985</v>
+        <v>0.884028620502364</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1p2</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>-1784.613388087789</v>
+        <v>-1775.584063373082</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.55**2 * Matern(length_scale=[0.11, 0.307, 1.07], nu=1.5) + WhiteKernel(noise_level=0.451)</t>
+          <t>0.712**2 * Matern(length_scale=[0.486, 12.1, 0.681, 2.39], nu=1.5) + WhiteKernel(noise_level=0.526)</t>
         </is>
       </c>
     </row>
@@ -673,25 +673,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1599609228712524</v>
+        <v>0.1649021271185886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2076219188567074</v>
+        <v>0.210773718692038</v>
       </c>
       <c r="G2" t="n">
-        <v>31.19237995989421</v>
+        <v>32.15591478812478</v>
       </c>
       <c r="H2" t="n">
-        <v>8.405837931999532</v>
+        <v>8.662984295797726</v>
       </c>
       <c r="I2" t="n">
-        <v>0.174229416394219</v>
+        <v>0.2027831479042894</v>
       </c>
       <c r="J2" t="n">
-        <v>0.982095372608896</v>
+        <v>0.9815476449622259</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2935780088748804</v>
+        <v>0.2990069640089872</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.213732607128729</v>
+        <v>0.2410075386846169</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4462548623963068</v>
+        <v>0.483393064687658</v>
       </c>
       <c r="G3" t="n">
-        <v>41.67785839010216</v>
+        <v>46.9964700435003</v>
       </c>
       <c r="H3" t="n">
-        <v>38.83296343140761</v>
+        <v>45.56542672268462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.203686989493951</v>
+        <v>0.2300603569486</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8187461541020428</v>
+        <v>0.7873222102130779</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2889258392928728</v>
+        <v>0.2962882329596978</v>
       </c>
     </row>
     <row r="4">
@@ -747,25 +747,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1994106365487125</v>
+        <v>0.2100183287905664</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3442575719422647</v>
+        <v>0.3557074807569559</v>
       </c>
       <c r="G4" t="n">
-        <v>38.88507412699893</v>
+        <v>40.95357411416045</v>
       </c>
       <c r="H4" t="n">
-        <v>23.11008878871879</v>
+        <v>24.67292331395973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2675214516297924</v>
+        <v>0.2897078592162587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8615231910373733</v>
+        <v>0.8521586083232804</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2877002130749804</v>
+        <v>0.2951991494376665</v>
       </c>
     </row>
     <row r="5">
@@ -784,25 +784,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1850074233043008</v>
+        <v>0.2023074471681567</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2719557781862316</v>
+        <v>0.2997835959441658</v>
       </c>
       <c r="G5" t="n">
-        <v>36.07644754433866</v>
+        <v>39.44995219779057</v>
       </c>
       <c r="H5" t="n">
-        <v>14.42218933133137</v>
+        <v>17.5246898574569</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2558743131315485</v>
+        <v>0.2835759533018062</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9099627632998619</v>
+        <v>0.8905939582026901</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2894154030857131</v>
+        <v>0.2955065433051439</v>
       </c>
     </row>
     <row r="6">
@@ -821,25 +821,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1970639302140431</v>
+        <v>0.2326833894813103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3000013020175643</v>
+        <v>0.3533594139023296</v>
       </c>
       <c r="G6" t="n">
-        <v>38.42746639173841</v>
+        <v>45.37326094885551</v>
       </c>
       <c r="H6" t="n">
-        <v>17.55015233638559</v>
+        <v>24.34826070171258</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2428666304820695</v>
+        <v>0.2891279587672202</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8348220300447718</v>
+        <v>0.7708398082499026</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2933028128648119</v>
+        <v>0.2972979539889631</v>
       </c>
     </row>
     <row r="7">
@@ -858,25 +858,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1297996970498443</v>
+        <v>0.1586334067647584</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1932882172973798</v>
+        <v>0.2401564641030697</v>
       </c>
       <c r="G7" t="n">
-        <v>25.31094092471963</v>
+        <v>30.93351431912789</v>
       </c>
       <c r="H7" t="n">
-        <v>7.285265314469828</v>
+        <v>11.24664981384535</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1978611168511706</v>
+        <v>0.2484151392453465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8805025922770828</v>
+        <v>0.8155255244235738</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2967555070288447</v>
+        <v>0.2994531551166428</v>
       </c>
     </row>
     <row r="8">
@@ -895,25 +895,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1327733642608811</v>
+        <v>0.1739279386569852</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1854525487682687</v>
+        <v>0.2456265001426386</v>
       </c>
       <c r="G8" t="n">
-        <v>25.89080603087181</v>
+        <v>33.91594803811211</v>
       </c>
       <c r="H8" t="n">
-        <v>6.706566329706177</v>
+        <v>11.76481362660272</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1763176733181888</v>
+        <v>0.2359866003422746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8695031453208337</v>
+        <v>0.7710794020842089</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3016856280978291</v>
+        <v>0.3045178619879248</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1p2</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
     </row>
@@ -1323,11 +1323,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
+          <t>alpha_jitter</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="22">
@@ -1336,11 +1336,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>random_state</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>42</v>
+          <t>residual_length_scale_floors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1349,11 +1351,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>autotune_cv_n_splits</t>
+          <t>n_restarts_optimizer</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1362,11 +1364,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>autotune_cv_restarts_optimizer</t>
+          <t>random_state</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
@@ -1375,12 +1377,64 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>autotune_cv_n_splits</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>autotune_cv_restarts_optimizer</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>grid_nx</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>grid_ny</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.55**2 * Matern(length_scale=[0.11, 0.307, 1.07], nu=1.5) + WhiteKernel(noise_level=0.451)</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.712**2 * Matern(length_scale=[0.486, 12.1, 0.681, 2.39], nu=1.5) + WhiteKernel(noise_level=0.526)</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,16 +1516,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1p2</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1486,22 +1540,22 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2312665518297267</v>
+        <v>0.2309654706121883</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3652099178500953</v>
+        <v>0.3651166741472622</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3011576792219494</v>
+        <v>0.3008122593727536</v>
       </c>
       <c r="J2" t="n">
-        <v>315.6788432475769</v>
+        <v>315.267867385637</v>
       </c>
       <c r="K2" t="n">
-        <v>182.0613577911402</v>
+        <v>181.9684035355888</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1221998454649152</v>
+        <v>0.1226480199752982</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1513,12 +1567,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>polar_matern32_ard_a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1533,22 +1587,22 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2318540852183289</v>
+        <v>0.2314550909289809</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3659309442717131</v>
+        <v>0.3656632507230045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3017831495594797</v>
+        <v>0.3012494894188602</v>
       </c>
       <c r="J3" t="n">
-        <v>316.480826323019</v>
+        <v>315.9361991180589</v>
       </c>
       <c r="K3" t="n">
-        <v>182.7809474066771</v>
+        <v>182.5136216485148</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1187303784490492</v>
+        <v>0.1200192768439259</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -1556,46 +1610,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>polar_matern52_ard_a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>cartesian_matern32_ard_a0p8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cartesian</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>matern32_ard</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2325630211390474</v>
+        <v>0.229463497921521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3667918512660616</v>
+        <v>0.364439315801028</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3024562654224805</v>
+        <v>0.3037147209962145</v>
       </c>
       <c r="J4" t="n">
-        <v>317.4485238547996</v>
+        <v>313.2176746628761</v>
       </c>
       <c r="K4" t="n">
-        <v>183.641997841827</v>
+        <v>181.2938603405767</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1145788648373347</v>
+        <v>0.1259002978227557</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1607,17 +1661,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cartesian_matern52_ard_a1</t>
+          <t>polar_rbf_ard_a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>rbf_ard</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1627,71 +1681,24 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2370428297641907</v>
+        <v>0.2332488857111363</v>
       </c>
       <c r="H5" t="n">
-        <v>0.373990149821096</v>
+        <v>0.3661064062191566</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3061788240317754</v>
+        <v>0.3072734969004929</v>
       </c>
       <c r="J5" t="n">
-        <v>323.5634626281203</v>
+        <v>318.384728995701</v>
       </c>
       <c r="K5" t="n">
-        <v>190.920682902776</v>
+        <v>182.9562744209738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07948503191841916</v>
+        <v>0.1178850476105281</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>cartesian_rbf_ard_a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cartesian</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rbf_ard</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.2411977941440828</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3755245418729</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.3170714112848412</v>
-      </c>
-      <c r="J6" t="n">
-        <v>329.234989006673</v>
-      </c>
-      <c r="K6" t="n">
-        <v>192.4905003141822</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.07191623213002529</v>
-      </c>
-      <c r="M6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1764,16 +1771,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>31.19237995989421</v>
+        <v>32.15591478812478</v>
       </c>
       <c r="E2" t="n">
-        <v>8.405837931999532</v>
+        <v>8.662984295797726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.174229416394219</v>
+        <v>0.2027831479042894</v>
       </c>
       <c r="G2" t="n">
-        <v>129.3311386450848</v>
+        <v>175.1958677393621</v>
       </c>
       <c r="H2" t="n">
         <v>4260.495759386248</v>
@@ -1792,16 +1799,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>41.67785839010216</v>
+        <v>46.9964700435003</v>
       </c>
       <c r="E3" t="n">
-        <v>38.83296343140761</v>
+        <v>45.56542672268462</v>
       </c>
       <c r="F3" t="n">
-        <v>0.203686989493951</v>
+        <v>0.2300603569486</v>
       </c>
       <c r="G3" t="n">
-        <v>228.7207965947854</v>
+        <v>291.7847935990236</v>
       </c>
       <c r="H3" t="n">
         <v>5512.886817461289</v>
@@ -1820,16 +1827,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>38.88507412699893</v>
+        <v>40.95357411416045</v>
       </c>
       <c r="E4" t="n">
-        <v>23.11008878871879</v>
+        <v>24.67292331395973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2675214516297924</v>
+        <v>0.2897078592162587</v>
       </c>
       <c r="G4" t="n">
-        <v>269.5737943337616</v>
+        <v>316.1411295747739</v>
       </c>
       <c r="H4" t="n">
         <v>3766.694924158668</v>
@@ -1848,16 +1855,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>36.07644754433866</v>
+        <v>39.44995219779057</v>
       </c>
       <c r="E5" t="n">
-        <v>14.42218933133137</v>
+        <v>17.5246898574569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2558743131315485</v>
+        <v>0.2835759533018062</v>
       </c>
       <c r="G5" t="n">
-        <v>1121.88709776819</v>
+        <v>1377.953541140899</v>
       </c>
       <c r="H5" t="n">
         <v>17135.46024586531</v>
@@ -1876,16 +1883,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>38.42746639173841</v>
+        <v>45.37326094885551</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55015233638559</v>
+        <v>24.34826070171258</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2428666304820695</v>
+        <v>0.2891279587672202</v>
       </c>
       <c r="G6" t="n">
-        <v>421.7820026772828</v>
+        <v>597.7678174596385</v>
       </c>
       <c r="H6" t="n">
         <v>7150.76242849565</v>
@@ -1904,16 +1911,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>25.31094092471963</v>
+        <v>30.93351431912789</v>
       </c>
       <c r="E7" t="n">
-        <v>7.285265314469828</v>
+        <v>11.24664981384535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1978611168511706</v>
+        <v>0.2484151392453465</v>
       </c>
       <c r="G7" t="n">
-        <v>266.4722788843321</v>
+        <v>420.0367050450863</v>
       </c>
       <c r="H7" t="n">
         <v>6806.614016268456</v>
@@ -1932,16 +1939,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>25.89080603087181</v>
+        <v>33.91594803811211</v>
       </c>
       <c r="E8" t="n">
-        <v>6.706566329706177</v>
+        <v>11.76481362660272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1763176733181888</v>
+        <v>0.2359866003422746</v>
       </c>
       <c r="G8" t="n">
-        <v>158.4779620088701</v>
+        <v>283.8911621744545</v>
       </c>
       <c r="H8" t="n">
         <v>5097.734174531417</v>
@@ -1957,16 +1964,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>237.4609733686638</v>
+        <v>269.7786344496716</v>
       </c>
       <c r="E9" t="n">
-        <v>116.3130634640189</v>
+        <v>143.7857483320596</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2284866245261445</v>
+        <v>0.2638759599380512</v>
       </c>
       <c r="G9" t="n">
-        <v>2596.245070912306</v>
+        <v>3462.771016733238</v>
       </c>
       <c r="H9" t="n">
         <v>49730.64836616704</v>
@@ -2073,13 +2080,13 @@
         <v>7.31</v>
       </c>
       <c r="I2" t="n">
-        <v>7.476525879302524</v>
+        <v>7.416313058692195</v>
       </c>
       <c r="J2" t="n">
         <v>4.5775</v>
       </c>
       <c r="K2" t="n">
-        <v>4.955840293758027</v>
+        <v>4.856366482755949</v>
       </c>
     </row>
     <row r="3">
@@ -2112,13 +2119,13 @@
         <v>6.66</v>
       </c>
       <c r="I3" t="n">
-        <v>6.676490420075641</v>
+        <v>6.798336326274096</v>
       </c>
       <c r="J3" t="n">
         <v>4.343333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>4.345822669377526</v>
+        <v>4.473445021820609</v>
       </c>
     </row>
     <row r="4">
@@ -2151,13 +2158,13 @@
         <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>6.795201677484906</v>
+        <v>6.753423150299891</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>4.605500966190041</v>
+        <v>4.615513042454795</v>
       </c>
     </row>
     <row r="5">
@@ -2190,13 +2197,13 @@
         <v>6.283</v>
       </c>
       <c r="I5" t="n">
-        <v>6.229528105002706</v>
+        <v>6.227028752787276</v>
       </c>
       <c r="J5" t="n">
         <v>4.354333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>4.31842388956668</v>
+        <v>4.290787507922803</v>
       </c>
     </row>
     <row r="6">
@@ -2225,13 +2232,13 @@
         <v>27.083</v>
       </c>
       <c r="I6" t="n">
-        <v>27.17774608186578</v>
+        <v>27.19510128805346</v>
       </c>
       <c r="J6" t="n">
         <v>6.77075</v>
       </c>
       <c r="K6" t="n">
-        <v>6.794436520466444</v>
+        <v>6.798775322013364</v>
       </c>
     </row>
     <row r="7">
@@ -2264,13 +2271,13 @@
         <v>3.672</v>
       </c>
       <c r="I7" t="n">
-        <v>1.454324539545475</v>
+        <v>1.323562369201061</v>
       </c>
       <c r="J7" t="n">
         <v>2.5935</v>
       </c>
       <c r="K7" t="n">
-        <v>1.014472824890764</v>
+        <v>0.9151030632087672</v>
       </c>
     </row>
     <row r="8">
@@ -2303,13 +2310,13 @@
         <v>3.598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.620393712614445</v>
+        <v>3.761384309891935</v>
       </c>
       <c r="J8" t="n">
         <v>2.582</v>
       </c>
       <c r="K8" t="n">
-        <v>2.634981338985013</v>
+        <v>2.750067219180605</v>
       </c>
     </row>
     <row r="9">
@@ -2342,13 +2349,13 @@
         <v>5.346</v>
       </c>
       <c r="I9" t="n">
-        <v>5.316685991761817</v>
+        <v>5.257965220609115</v>
       </c>
       <c r="J9" t="n">
         <v>3.14975</v>
       </c>
       <c r="K9" t="n">
-        <v>3.207948470404995</v>
+        <v>3.217130833092028</v>
       </c>
     </row>
     <row r="10">
@@ -2381,13 +2388,13 @@
         <v>3.606</v>
       </c>
       <c r="I10" t="n">
-        <v>3.700820289869358</v>
+        <v>3.648098002638617</v>
       </c>
       <c r="J10" t="n">
         <v>2.422666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.495864142110388</v>
+        <v>2.459096328123566</v>
       </c>
     </row>
     <row r="11">
@@ -2416,13 +2423,13 @@
         <v>16.222</v>
       </c>
       <c r="I11" t="n">
-        <v>14.0922245337911</v>
+        <v>13.99100990234073</v>
       </c>
       <c r="J11" t="n">
         <v>4.0555</v>
       </c>
       <c r="K11" t="n">
-        <v>3.523056133447774</v>
+        <v>3.497752475585183</v>
       </c>
     </row>
     <row r="12">
@@ -2455,13 +2462,13 @@
         <v>3.322</v>
       </c>
       <c r="I12" t="n">
-        <v>3.832138595743121</v>
+        <v>3.699765616822507</v>
       </c>
       <c r="J12" t="n">
         <v>1.951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.202976714070778</v>
+        <v>2.128312593961923</v>
       </c>
     </row>
     <row r="13">
@@ -2494,13 +2501,13 @@
         <v>2.395</v>
       </c>
       <c r="I13" t="n">
-        <v>2.764601943485029</v>
+        <v>2.889844066610538</v>
       </c>
       <c r="J13" t="n">
         <v>1.944333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.868085068159688</v>
+        <v>1.963869488396502</v>
       </c>
     </row>
     <row r="14">
@@ -2533,13 +2540,13 @@
         <v>3.389</v>
       </c>
       <c r="I14" t="n">
-        <v>3.489512180831612</v>
+        <v>3.427444919494758</v>
       </c>
       <c r="J14" t="n">
         <v>2.5625</v>
       </c>
       <c r="K14" t="n">
-        <v>2.60080532037223</v>
+        <v>2.610225752755173</v>
       </c>
     </row>
     <row r="15">
@@ -2572,13 +2579,13 @@
         <v>2.734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.769828841677883</v>
+        <v>2.700786222511771</v>
       </c>
       <c r="J15" t="n">
         <v>1.724</v>
       </c>
       <c r="K15" t="n">
-        <v>1.973411989177132</v>
+        <v>1.924181766351929</v>
       </c>
     </row>
     <row r="16">
@@ -2607,13 +2614,13 @@
         <v>11.84</v>
       </c>
       <c r="I16" t="n">
-        <v>12.85608156173765</v>
+        <v>12.71784082543957</v>
       </c>
       <c r="J16" t="n">
         <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.214020390434412</v>
+        <v>3.179460206359893</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2653,13 @@
         <v>2.997</v>
       </c>
       <c r="I17" t="n">
-        <v>1.914503382009573</v>
+        <v>1.930458679100686</v>
       </c>
       <c r="J17" t="n">
         <v>1.869</v>
       </c>
       <c r="K17" t="n">
-        <v>1.563130451942294</v>
+        <v>1.550853678705982</v>
       </c>
     </row>
     <row r="18">
@@ -2685,13 +2692,13 @@
         <v>2.182</v>
       </c>
       <c r="I18" t="n">
-        <v>2.138621754066468</v>
+        <v>2.286937626166762</v>
       </c>
       <c r="J18" t="n">
         <v>1.721</v>
       </c>
       <c r="K18" t="n">
-        <v>1.473130127962245</v>
+        <v>1.541724564113339</v>
       </c>
     </row>
     <row r="19">
@@ -2724,13 +2731,13 @@
         <v>3.611</v>
       </c>
       <c r="I19" t="n">
-        <v>3.378040641683027</v>
+        <v>3.385159081661953</v>
       </c>
       <c r="J19" t="n">
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>2.537362085778801</v>
+        <v>2.550563712863219</v>
       </c>
     </row>
     <row r="20">
@@ -2763,13 +2770,13 @@
         <v>3.509</v>
       </c>
       <c r="I20" t="n">
-        <v>3.207650276220559</v>
+        <v>3.113250383602602</v>
       </c>
       <c r="J20" t="n">
         <v>1.865</v>
       </c>
       <c r="K20" t="n">
-        <v>1.376418938160967</v>
+        <v>1.305412026478876</v>
       </c>
     </row>
     <row r="21">
@@ -2798,13 +2805,13 @@
         <v>12.299</v>
       </c>
       <c r="I21" t="n">
-        <v>10.63881605397963</v>
+        <v>10.715805770532</v>
       </c>
       <c r="J21" t="n">
         <v>3.07475</v>
       </c>
       <c r="K21" t="n">
-        <v>2.659704013494907</v>
+        <v>2.678951442633001</v>
       </c>
     </row>
     <row r="22">
@@ -2837,13 +2844,13 @@
         <v>2.954</v>
       </c>
       <c r="I22" t="n">
-        <v>2.860359307139779</v>
+        <v>2.961688890578897</v>
       </c>
       <c r="J22" t="n">
         <v>2.02725</v>
       </c>
       <c r="K22" t="n">
-        <v>2.284597290383344</v>
+        <v>2.356474878304748</v>
       </c>
     </row>
     <row r="23">
@@ -2876,13 +2883,13 @@
         <v>2.144</v>
       </c>
       <c r="I23" t="n">
-        <v>2.095830825515689</v>
+        <v>2.286964638287909</v>
       </c>
       <c r="J23" t="n">
         <v>1.503666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.696126347992624</v>
+        <v>1.771202297030148</v>
       </c>
     </row>
     <row r="24">
@@ -2915,13 +2922,13 @@
         <v>1.642</v>
       </c>
       <c r="I24" t="n">
-        <v>1.898045358770527</v>
+        <v>1.953045172332649</v>
       </c>
       <c r="J24" t="n">
         <v>1.25525</v>
       </c>
       <c r="K24" t="n">
-        <v>1.245369045413602</v>
+        <v>1.27316742326134</v>
       </c>
     </row>
     <row r="25">
@@ -2954,13 +2961,13 @@
         <v>2.317</v>
       </c>
       <c r="I25" t="n">
-        <v>2.466319910705371</v>
+        <v>2.337749728686704</v>
       </c>
       <c r="J25" t="n">
         <v>1.458</v>
       </c>
       <c r="K25" t="n">
-        <v>1.773853644440454</v>
+        <v>1.713087421550177</v>
       </c>
     </row>
     <row r="26">
@@ -2989,13 +2996,13 @@
         <v>9.057</v>
       </c>
       <c r="I26" t="n">
-        <v>9.320555402131367</v>
+        <v>9.539448429886159</v>
       </c>
       <c r="J26" t="n">
         <v>2.26425</v>
       </c>
       <c r="K26" t="n">
-        <v>2.330138850532842</v>
+        <v>2.38486210747154</v>
       </c>
     </row>
     <row r="27">
@@ -3028,13 +3035,13 @@
         <v>2.598</v>
       </c>
       <c r="I27" t="n">
-        <v>2.315683415185462</v>
+        <v>2.350909118958581</v>
       </c>
       <c r="J27" t="n">
         <v>1.5755</v>
       </c>
       <c r="K27" t="n">
-        <v>1.499646312284661</v>
+        <v>1.538046333577959</v>
       </c>
     </row>
     <row r="28">
@@ -3067,13 +3074,13 @@
         <v>1.464</v>
       </c>
       <c r="I28" t="n">
-        <v>1.781553234172052</v>
+        <v>1.9341557894611</v>
       </c>
       <c r="J28" t="n">
         <v>1.202666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.589607214387804</v>
+        <v>1.682781915305274</v>
       </c>
     </row>
     <row r="29">
@@ -3106,13 +3113,13 @@
         <v>1.402</v>
       </c>
       <c r="I29" t="n">
-        <v>1.501361145226651</v>
+        <v>1.527779455398029</v>
       </c>
       <c r="J29" t="n">
         <v>1.1765</v>
       </c>
       <c r="K29" t="n">
-        <v>1.189393563793123</v>
+        <v>1.264480872067553</v>
       </c>
     </row>
     <row r="30">
@@ -3145,13 +3152,13 @@
         <v>2.042</v>
       </c>
       <c r="I30" t="n">
-        <v>1.938648859068834</v>
+        <v>1.780429802997515</v>
       </c>
       <c r="J30" t="n">
         <v>1.508666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.312884299966541</v>
+        <v>1.17926914763693</v>
       </c>
     </row>
     <row r="31">
@@ -3180,13 +3187,13 @@
         <v>7.505999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>7.537246653652999</v>
+        <v>7.593274166815225</v>
       </c>
       <c r="J31" t="n">
         <v>1.8765</v>
       </c>
       <c r="K31" t="n">
-        <v>1.88431166341325</v>
+        <v>1.898318541703806</v>
       </c>
     </row>
     <row r="32">
@@ -3219,13 +3226,13 @@
         <v>2.347</v>
       </c>
       <c r="I32" t="n">
-        <v>1.702759629696386</v>
+        <v>1.613707493165421</v>
       </c>
       <c r="J32" t="n">
         <v>1.196</v>
       </c>
       <c r="K32" t="n">
-        <v>1.21864647595188</v>
+        <v>1.210334758106222</v>
       </c>
     </row>
     <row r="33">
@@ -3258,13 +3265,13 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.29711322299346</v>
+        <v>1.490481394676311</v>
       </c>
       <c r="J33" t="n">
         <v>0.8406666666666668</v>
       </c>
       <c r="K33" t="n">
-        <v>0.996516763459641</v>
+        <v>1.069196562412963</v>
       </c>
     </row>
     <row r="34">
@@ -3297,13 +3304,13 @@
         <v>1.481</v>
       </c>
       <c r="I34" t="n">
-        <v>1.698462088683069</v>
+        <v>1.682635643035865</v>
       </c>
       <c r="J34" t="n">
         <v>0.7117500000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8214108862962035</v>
+        <v>0.9073546471057639</v>
       </c>
     </row>
     <row r="35">
@@ -3336,13 +3343,13 @@
         <v>1.458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.328832505473375</v>
+        <v>1.198897805881131</v>
       </c>
       <c r="J35" t="n">
         <v>0.9506666666666668</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8755585909258249</v>
+        <v>0.7448227346518818</v>
       </c>
     </row>
     <row r="36">
@@ -3371,13 +3378,13 @@
         <v>6.886</v>
       </c>
       <c r="I36" t="n">
-        <v>6.02716744684629</v>
+        <v>5.985722336758728</v>
       </c>
       <c r="J36" t="n">
         <v>1.7215</v>
       </c>
       <c r="K36" t="n">
-        <v>1.506791861711573</v>
+        <v>1.496430584189682</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/Four_Fan_Annular_GP/four_annular_gp_summary.xlsx
+++ b/01_Thermal/B_results/Four_Fan_Annular_GP/four_annular_gp_summary.xlsx
@@ -526,22 +526,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1976400252378546</v>
+        <v>0.1871467398898145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3245574595747438</v>
+        <v>0.2896507761224122</v>
       </c>
       <c r="D2" t="n">
-        <v>269.7786344496716</v>
+        <v>255.4552999495967</v>
       </c>
       <c r="E2" t="n">
-        <v>143.7857483320596</v>
+        <v>114.520185927851</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2638759599380512</v>
+        <v>0.2412000056873755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.884028620502364</v>
+        <v>0.9076329601755295</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
@@ -553,18 +553,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>matern32_ard</t>
+          <t>matern52_ard</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>polar_matern32_ard_a1p2</t>
+          <t>polar_matern52_ard_a1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>-1775.584063373082</v>
+        <v>-1819.876603975742</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.712**2 * Matern(length_scale=[0.486, 12.1, 0.681, 2.39], nu=1.5) + WhiteKernel(noise_level=0.526)</t>
+          <t>0.789**2 * Matern(length_scale=[0.486, 100, 0.681, 1.96], nu=2.5) + WhiteKernel(noise_level=0.64)</t>
         </is>
       </c>
     </row>
@@ -673,25 +673,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1649021271185886</v>
+        <v>0.1518502127842798</v>
       </c>
       <c r="F2" t="n">
-        <v>0.210773718692038</v>
+        <v>0.198404419280849</v>
       </c>
       <c r="G2" t="n">
-        <v>32.15591478812478</v>
+        <v>29.61079149293456</v>
       </c>
       <c r="H2" t="n">
-        <v>8.662984295797726</v>
+        <v>7.676041150083327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2027831479042894</v>
+        <v>0.1739226652479511</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9815476449622259</v>
+        <v>0.9836498564756018</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2990069640089872</v>
+        <v>0.2977331676334183</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2410075386846169</v>
+        <v>0.1697105567776049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.483393064687658</v>
+        <v>0.2500956702336073</v>
       </c>
       <c r="G3" t="n">
-        <v>46.9964700435003</v>
+        <v>33.09355857163295</v>
       </c>
       <c r="H3" t="n">
-        <v>45.56542672268462</v>
+        <v>12.19682963257146</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2300603569486</v>
+        <v>0.1938661123783066</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7873222102130779</v>
+        <v>0.9430709870347483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2962882329596978</v>
+        <v>0.2950574372450656</v>
       </c>
     </row>
     <row r="4">
@@ -747,25 +747,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2100183287905664</v>
+        <v>0.2058975394407748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3557074807569559</v>
+        <v>0.3602837862046097</v>
       </c>
       <c r="G4" t="n">
-        <v>40.95357411416045</v>
+        <v>40.15002019095108</v>
       </c>
       <c r="H4" t="n">
-        <v>24.67292331395973</v>
+        <v>25.31185928737613</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2897078592162587</v>
+        <v>0.2961371082853932</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8521586083232804</v>
+        <v>0.8483300719840637</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2951991494376665</v>
+        <v>0.2940383312165001</v>
       </c>
     </row>
     <row r="5">
@@ -784,25 +784,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2023074471681567</v>
+        <v>0.2007480315229926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2997835959441658</v>
+        <v>0.3081046178287488</v>
       </c>
       <c r="G5" t="n">
-        <v>39.44995219779057</v>
+        <v>39.14586614698355</v>
       </c>
       <c r="H5" t="n">
-        <v>17.5246898574569</v>
+        <v>18.51104882784288</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2835759533018062</v>
+        <v>0.232809797164752</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8905939582026901</v>
+        <v>0.8844361527511271</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2955065433051439</v>
+        <v>0.2944168345011332</v>
       </c>
     </row>
     <row r="6">
@@ -821,25 +821,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2326833894813103</v>
+        <v>0.2349449233963989</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3533594139023296</v>
+        <v>0.3614119260900229</v>
       </c>
       <c r="G6" t="n">
-        <v>45.37326094885551</v>
+        <v>45.81426006229779</v>
       </c>
       <c r="H6" t="n">
-        <v>24.34826070171258</v>
+        <v>25.47062316241953</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2891279587672202</v>
+        <v>0.2955108553159919</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7708398082499026</v>
+        <v>0.7602763926589636</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2972979539889631</v>
+        <v>0.2961506043156089</v>
       </c>
     </row>
     <row r="7">
@@ -858,25 +858,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1586334067647584</v>
+        <v>0.1642345939872336</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2401564641030697</v>
+        <v>0.2550099867918659</v>
       </c>
       <c r="G7" t="n">
-        <v>30.93351431912789</v>
+        <v>32.02574582751055</v>
       </c>
       <c r="H7" t="n">
-        <v>11.24664981384535</v>
+        <v>12.68086820589958</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2484151392453465</v>
+        <v>0.2692015255195721</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8155255244235738</v>
+        <v>0.7920005912109688</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2994531551166428</v>
+        <v>0.2981221884708575</v>
       </c>
     </row>
     <row r="8">
@@ -895,25 +895,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1739279386569852</v>
+        <v>0.1826413213194165</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2456265001426386</v>
+        <v>0.2549300121316163</v>
       </c>
       <c r="G8" t="n">
-        <v>33.91594803811211</v>
+        <v>35.61505765728622</v>
       </c>
       <c r="H8" t="n">
-        <v>11.76481362660272</v>
+        <v>12.67291566165808</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2359866003422746</v>
+        <v>0.2328597585383104</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7710794020842089</v>
+        <v>0.7534094867390689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3045178619879248</v>
+        <v>0.3026729517209882</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,11 +1142,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>overlap_ratio_threshold</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1.25</v>
+          <t>sigma_mapping_method</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sampled_fan_average_inheritance_distance_blend + z_pchip_hold_bounds</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1155,11 +1157,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>overlap_weight_power</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
+          <t>feature_mode</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1168,11 +1172,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>overlap_sigma_boost</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1.12</v>
+          <t>kernel_family</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1181,13 +1187,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>feature_mode</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>polar</t>
-        </is>
+          <t>alpha_scale</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1196,13 +1200,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kernel_family</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>matern32_ard</t>
-        </is>
+          <t>autotune_enabled</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1211,11 +1213,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>alpha_scale</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1.2</v>
+          <t>autotune_selected</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>polar_matern52_ard_a1</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1224,11 +1228,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>autotune_enabled</t>
-        </is>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
+          <t>mean_function</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>harmonic_annular_bemt</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1237,12 +1243,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>autotune_selected</t>
+          <t>mean_params_xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>polar_matern32_ard_a1p2</t>
+          <t>B_results\four_annular_bemt_params_pchip.xlsx</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1258,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mean_function</t>
+          <t>mean_params_sheet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>harmonic_annular_bemt</t>
+          <t>four_bemt_az_pchip</t>
         </is>
       </c>
     </row>
@@ -1267,13 +1273,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mean_params_xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B_results\four_annular_bemt_params_pchip.xlsx</t>
-        </is>
+          <t>sigma_fallback_mps</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
@@ -1282,13 +1286,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mean_params_sheet</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>four_bemt_az_pchip</t>
-        </is>
+          <t>sigma_min_mps</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -1297,11 +1299,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sigma_fallback_mps</t>
+          <t>alpha_jitter</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.14</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="20">
@@ -1310,11 +1312,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sigma_min_mps</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.03</v>
+          <t>residual_length_scale_floors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1323,11 +1327,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>alpha_jitter</t>
+          <t>n_restarts_optimizer</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1e-08</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1336,13 +1340,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>residual_length_scale_floors</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
-        </is>
+          <t>random_state</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1351,11 +1353,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
+          <t>autotune_cv_n_splits</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1364,11 +1366,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>random_state</t>
+          <t>autotune_cv_restarts_optimizer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1377,11 +1379,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>autotune_cv_n_splits</t>
+          <t>grid_nx</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26">
@@ -1390,11 +1392,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>autotune_cv_restarts_optimizer</t>
+          <t>grid_ny</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
@@ -1403,11 +1405,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>grid_nx</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>240</v>
+          <t>overall_fluctuation_rule</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sqrt(sigma_fluc_mps^2 + w_pred_std_mps^2)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1416,25 +1420,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>grid_ny</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0.712**2 * Matern(length_scale=[0.486, 12.1, 0.681, 2.39], nu=1.5) + WhiteKernel(noise_level=0.526)</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.789**2 * Matern(length_scale=[0.486, 100, 0.681, 1.96], nu=2.5) + WhiteKernel(noise_level=0.64)</t>
         </is>
       </c>
     </row>
@@ -1516,46 +1507,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>polar_matern52_ard_a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>polar_matern32_ard_a1p2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>polar</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>matern32_ard</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.2</v>
-      </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2309654706121883</v>
+        <v>0.2060911882598105</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3651166741472622</v>
+        <v>0.3144971244029336</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3008122593727536</v>
+        <v>0.2665996075448042</v>
       </c>
       <c r="J2" t="n">
-        <v>315.267867385637</v>
+        <v>281.3144719746414</v>
       </c>
       <c r="K2" t="n">
-        <v>181.9684035355888</v>
+        <v>135.01002231678</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1226480199752982</v>
+        <v>0.2205638299877813</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1563,11 +1554,11 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polar_matern32_ard_a1</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1581,28 +1572,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2314550909289809</v>
+        <v>0.2066415770198992</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3656632507230045</v>
+        <v>0.315844789902492</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3012494894188602</v>
+        <v>0.2705252003075975</v>
       </c>
       <c r="J3" t="n">
-        <v>315.9361991180589</v>
+        <v>282.0657526321623</v>
       </c>
       <c r="K3" t="n">
-        <v>182.5136216485148</v>
+        <v>136.1695762361698</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1200192768439259</v>
+        <v>0.2138695249995843</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -1610,11 +1601,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>polar_matern52_ard_a1</t>
+          <t>polar_rbf_ard_a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1624,7 +1615,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>rbf_ard</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1634,22 +1625,22 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.229463497921521</v>
+        <v>0.2109680363832973</v>
       </c>
       <c r="H4" t="n">
-        <v>0.364439315801028</v>
+        <v>0.3190746103479307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3037147209962145</v>
+        <v>0.2714302731073098</v>
       </c>
       <c r="J4" t="n">
-        <v>313.2176746628761</v>
+        <v>287.9713696632008</v>
       </c>
       <c r="K4" t="n">
-        <v>181.2938603405767</v>
+        <v>138.9687485122533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1259002978227557</v>
+        <v>0.1977094201374746</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1657,11 +1648,11 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>polar_rbf_ard_a1</t>
+          <t>polar_matern32_ard_a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1671,7 +1662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rbf_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1681,22 +1672,22 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2332488857111363</v>
+        <v>0.2079033389694928</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3661064062191566</v>
+        <v>0.3162301654208309</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3072734969004929</v>
+        <v>0.2716158625144873</v>
       </c>
       <c r="J5" t="n">
-        <v>318.384728995701</v>
+        <v>283.7880576933577</v>
       </c>
       <c r="K5" t="n">
-        <v>182.9562744209738</v>
+        <v>136.5020714176475</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1178850476105281</v>
+        <v>0.2119499729074412</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -1771,19 +1762,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>32.15591478812478</v>
+        <v>29.61079149293456</v>
       </c>
       <c r="E2" t="n">
-        <v>8.662984295797726</v>
+        <v>7.676041150083327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2027831479042894</v>
+        <v>0.1739226652479511</v>
       </c>
       <c r="G2" t="n">
-        <v>175.1958677393621</v>
+        <v>133.2232349318846</v>
       </c>
       <c r="H2" t="n">
-        <v>4260.495759386248</v>
+        <v>4404.205864527997</v>
       </c>
     </row>
     <row r="3">
@@ -1799,19 +1790,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>46.9964700435003</v>
+        <v>33.09355857163295</v>
       </c>
       <c r="E3" t="n">
-        <v>45.56542672268462</v>
+        <v>12.19682963257146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2300603569486</v>
+        <v>0.1938661123783066</v>
       </c>
       <c r="G3" t="n">
-        <v>291.7847935990236</v>
+        <v>277.2497042747839</v>
       </c>
       <c r="H3" t="n">
-        <v>5512.886817461289</v>
+        <v>7376.787765444902</v>
       </c>
     </row>
     <row r="4">
@@ -1827,19 +1818,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>40.95357411416045</v>
+        <v>40.15002019095108</v>
       </c>
       <c r="E4" t="n">
-        <v>24.67292331395973</v>
+        <v>25.31185928737613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2897078592162587</v>
+        <v>0.2961371082853932</v>
       </c>
       <c r="G4" t="n">
-        <v>316.1411295747739</v>
+        <v>293.3429531072492</v>
       </c>
       <c r="H4" t="n">
-        <v>3766.694924158668</v>
+        <v>3344.952825335054</v>
       </c>
     </row>
     <row r="5">
@@ -1855,19 +1846,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44995219779057</v>
+        <v>39.14586614698355</v>
       </c>
       <c r="E5" t="n">
-        <v>17.5246898574569</v>
+        <v>18.51104882784288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2835759533018062</v>
+        <v>0.232809797164752</v>
       </c>
       <c r="G5" t="n">
-        <v>1377.953541140899</v>
+        <v>1686.781042783403</v>
       </c>
       <c r="H5" t="n">
-        <v>17135.46024586531</v>
+        <v>31121.19082608325</v>
       </c>
     </row>
     <row r="6">
@@ -1883,19 +1874,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>45.37326094885551</v>
+        <v>45.81426006229779</v>
       </c>
       <c r="E6" t="n">
-        <v>24.34826070171258</v>
+        <v>25.47062316241953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2891279587672202</v>
+        <v>0.2955108553159919</v>
       </c>
       <c r="G6" t="n">
-        <v>597.7678174596385</v>
+        <v>682.2261745354665</v>
       </c>
       <c r="H6" t="n">
-        <v>7150.76242849565</v>
+        <v>7812.346546992781</v>
       </c>
     </row>
     <row r="7">
@@ -1911,19 +1902,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>30.93351431912789</v>
+        <v>32.02574582751055</v>
       </c>
       <c r="E7" t="n">
-        <v>11.24664981384535</v>
+        <v>12.68086820589958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2484151392453465</v>
+        <v>0.2692015255195721</v>
       </c>
       <c r="G7" t="n">
-        <v>420.0367050450863</v>
+        <v>505.9608597230443</v>
       </c>
       <c r="H7" t="n">
-        <v>6806.614016268456</v>
+        <v>6981.71133541129</v>
       </c>
     </row>
     <row r="8">
@@ -1939,19 +1930,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>33.91594803811211</v>
+        <v>35.61505765728622</v>
       </c>
       <c r="E8" t="n">
-        <v>11.76481362660272</v>
+        <v>12.67291566165808</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2359866003422746</v>
+        <v>0.2328597585383104</v>
       </c>
       <c r="G8" t="n">
-        <v>283.8911621744545</v>
+        <v>378.0146196540255</v>
       </c>
       <c r="H8" t="n">
-        <v>5097.734174531417</v>
+        <v>6971.395325081485</v>
       </c>
     </row>
     <row r="9">
@@ -1964,19 +1955,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>269.7786344496716</v>
+        <v>255.4552999495967</v>
       </c>
       <c r="E9" t="n">
-        <v>143.7857483320596</v>
+        <v>114.520185927851</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2638759599380512</v>
+        <v>0.2412000056873754</v>
       </c>
       <c r="G9" t="n">
-        <v>3462.771016733238</v>
+        <v>3956.798589009857</v>
       </c>
       <c r="H9" t="n">
-        <v>49730.64836616704</v>
+        <v>68012.59048887675</v>
       </c>
     </row>
   </sheetData>
@@ -2080,13 +2071,13 @@
         <v>7.31</v>
       </c>
       <c r="I2" t="n">
-        <v>7.416313058692195</v>
+        <v>7.262421844630803</v>
       </c>
       <c r="J2" t="n">
         <v>4.5775</v>
       </c>
       <c r="K2" t="n">
-        <v>4.856366482755949</v>
+        <v>4.690283786621561</v>
       </c>
     </row>
     <row r="3">
@@ -2119,13 +2110,13 @@
         <v>6.66</v>
       </c>
       <c r="I3" t="n">
-        <v>6.798336326274096</v>
+        <v>6.663950711867259</v>
       </c>
       <c r="J3" t="n">
         <v>4.343333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>4.473445021820609</v>
+        <v>4.297251612024504</v>
       </c>
     </row>
     <row r="4">
@@ -2158,13 +2149,13 @@
         <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>6.753423150299891</v>
+        <v>6.766629045556486</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>4.615513042454795</v>
+        <v>4.619977877016016</v>
       </c>
     </row>
     <row r="5">
@@ -2197,13 +2188,13 @@
         <v>6.283</v>
       </c>
       <c r="I5" t="n">
-        <v>6.227028752787276</v>
+        <v>6.232966229963702</v>
       </c>
       <c r="J5" t="n">
         <v>4.354333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>4.290787507922803</v>
+        <v>4.28650199599848</v>
       </c>
     </row>
     <row r="6">
@@ -2232,13 +2223,13 @@
         <v>27.083</v>
       </c>
       <c r="I6" t="n">
-        <v>27.19510128805346</v>
+        <v>26.92596783201825</v>
       </c>
       <c r="J6" t="n">
         <v>6.77075</v>
       </c>
       <c r="K6" t="n">
-        <v>6.798775322013364</v>
+        <v>6.731491958004562</v>
       </c>
     </row>
     <row r="7">
@@ -2271,13 +2262,13 @@
         <v>3.672</v>
       </c>
       <c r="I7" t="n">
-        <v>1.323562369201061</v>
+        <v>4.276640412387382</v>
       </c>
       <c r="J7" t="n">
         <v>2.5935</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9151030632087672</v>
+        <v>2.80031568723358</v>
       </c>
     </row>
     <row r="8">
@@ -2310,13 +2301,13 @@
         <v>3.598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.761384309891935</v>
+        <v>3.777747576197674</v>
       </c>
       <c r="J8" t="n">
         <v>2.582</v>
       </c>
       <c r="K8" t="n">
-        <v>2.750067219180605</v>
+        <v>2.655884321366758</v>
       </c>
     </row>
     <row r="9">
@@ -2349,13 +2340,13 @@
         <v>5.346</v>
       </c>
       <c r="I9" t="n">
-        <v>5.257965220609115</v>
+        <v>5.191660021051662</v>
       </c>
       <c r="J9" t="n">
         <v>3.14975</v>
       </c>
       <c r="K9" t="n">
-        <v>3.217130833092028</v>
+        <v>3.237974533041915</v>
       </c>
     </row>
     <row r="10">
@@ -2388,13 +2379,13 @@
         <v>3.606</v>
       </c>
       <c r="I10" t="n">
-        <v>3.648098002638617</v>
+        <v>3.634554573973266</v>
       </c>
       <c r="J10" t="n">
         <v>2.422666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.459096328123566</v>
+        <v>2.457184822530936</v>
       </c>
     </row>
     <row r="11">
@@ -2423,13 +2414,13 @@
         <v>16.222</v>
       </c>
       <c r="I11" t="n">
-        <v>13.99100990234073</v>
+        <v>16.88060258360998</v>
       </c>
       <c r="J11" t="n">
         <v>4.0555</v>
       </c>
       <c r="K11" t="n">
-        <v>3.497752475585183</v>
+        <v>4.220150645902496</v>
       </c>
     </row>
     <row r="12">
@@ -2462,13 +2453,13 @@
         <v>3.322</v>
       </c>
       <c r="I12" t="n">
-        <v>3.699765616822507</v>
+        <v>3.510197976209843</v>
       </c>
       <c r="J12" t="n">
         <v>1.951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.128312593961923</v>
+        <v>2.043109588069425</v>
       </c>
     </row>
     <row r="13">
@@ -2501,13 +2492,13 @@
         <v>2.395</v>
       </c>
       <c r="I13" t="n">
-        <v>2.889844066610538</v>
+        <v>2.74261620423144</v>
       </c>
       <c r="J13" t="n">
         <v>1.944333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.963869488396502</v>
+        <v>1.892508859362436</v>
       </c>
     </row>
     <row r="14">
@@ -2540,13 +2531,13 @@
         <v>3.389</v>
       </c>
       <c r="I14" t="n">
-        <v>3.427444919494758</v>
+        <v>3.516080024994547</v>
       </c>
       <c r="J14" t="n">
         <v>2.5625</v>
       </c>
       <c r="K14" t="n">
-        <v>2.610225752755173</v>
+        <v>2.615041999425389</v>
       </c>
     </row>
     <row r="15">
@@ -2579,13 +2570,13 @@
         <v>2.734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.700786222511771</v>
+        <v>2.707806827751252</v>
       </c>
       <c r="J15" t="n">
         <v>1.724</v>
       </c>
       <c r="K15" t="n">
-        <v>1.924181766351929</v>
+        <v>1.919001198772917</v>
       </c>
     </row>
     <row r="16">
@@ -2614,13 +2605,13 @@
         <v>11.84</v>
       </c>
       <c r="I16" t="n">
-        <v>12.71784082543957</v>
+        <v>12.47670103318708</v>
       </c>
       <c r="J16" t="n">
         <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.179460206359893</v>
+        <v>3.11917525829677</v>
       </c>
     </row>
     <row r="17">
@@ -2653,13 +2644,13 @@
         <v>2.997</v>
       </c>
       <c r="I17" t="n">
-        <v>1.930458679100686</v>
+        <v>1.845216697797918</v>
       </c>
       <c r="J17" t="n">
         <v>1.869</v>
       </c>
       <c r="K17" t="n">
-        <v>1.550853678705982</v>
+        <v>1.418438509795242</v>
       </c>
     </row>
     <row r="18">
@@ -2692,13 +2683,13 @@
         <v>2.182</v>
       </c>
       <c r="I18" t="n">
-        <v>2.286937626166762</v>
+        <v>2.243728583282373</v>
       </c>
       <c r="J18" t="n">
         <v>1.721</v>
       </c>
       <c r="K18" t="n">
-        <v>1.541724564113339</v>
+        <v>1.50251267440467</v>
       </c>
     </row>
     <row r="19">
@@ -2731,13 +2722,13 @@
         <v>3.611</v>
       </c>
       <c r="I19" t="n">
-        <v>3.385159081661953</v>
+        <v>3.252459065951223</v>
       </c>
       <c r="J19" t="n">
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>2.550563712863219</v>
+        <v>2.535837833854575</v>
       </c>
     </row>
     <row r="20">
@@ -2770,13 +2761,13 @@
         <v>3.509</v>
       </c>
       <c r="I20" t="n">
-        <v>3.113250383602602</v>
+        <v>3.032461437023099</v>
       </c>
       <c r="J20" t="n">
         <v>1.865</v>
       </c>
       <c r="K20" t="n">
-        <v>1.305412026478876</v>
+        <v>1.292481851172171</v>
       </c>
     </row>
     <row r="21">
@@ -2805,13 +2796,13 @@
         <v>12.299</v>
       </c>
       <c r="I21" t="n">
-        <v>10.715805770532</v>
+        <v>10.37386578405461</v>
       </c>
       <c r="J21" t="n">
         <v>3.07475</v>
       </c>
       <c r="K21" t="n">
-        <v>2.678951442633001</v>
+        <v>2.593466446013653</v>
       </c>
     </row>
     <row r="22">
@@ -2844,13 +2835,13 @@
         <v>2.954</v>
       </c>
       <c r="I22" t="n">
-        <v>2.961688890578897</v>
+        <v>2.941123486493395</v>
       </c>
       <c r="J22" t="n">
         <v>2.02725</v>
       </c>
       <c r="K22" t="n">
-        <v>2.356474878304748</v>
+        <v>2.363427234342201</v>
       </c>
     </row>
     <row r="23">
@@ -2883,13 +2874,13 @@
         <v>2.144</v>
       </c>
       <c r="I23" t="n">
-        <v>2.286964638287909</v>
+        <v>2.418840042986725</v>
       </c>
       <c r="J23" t="n">
         <v>1.503666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.771202297030148</v>
+        <v>1.834562837050476</v>
       </c>
     </row>
     <row r="24">
@@ -2922,13 +2913,13 @@
         <v>1.642</v>
       </c>
       <c r="I24" t="n">
-        <v>1.953045172332649</v>
+        <v>2.036429048358384</v>
       </c>
       <c r="J24" t="n">
         <v>1.25525</v>
       </c>
       <c r="K24" t="n">
-        <v>1.27316742326134</v>
+        <v>1.279541838328937</v>
       </c>
     </row>
     <row r="25">
@@ -2961,13 +2952,13 @@
         <v>2.317</v>
       </c>
       <c r="I25" t="n">
-        <v>2.337749728686704</v>
+        <v>2.307252486341163</v>
       </c>
       <c r="J25" t="n">
         <v>1.458</v>
       </c>
       <c r="K25" t="n">
-        <v>1.713087421550177</v>
+        <v>1.715852888649882</v>
       </c>
     </row>
     <row r="26">
@@ -2996,13 +2987,13 @@
         <v>9.057</v>
       </c>
       <c r="I26" t="n">
-        <v>9.539448429886159</v>
+        <v>9.703645064179668</v>
       </c>
       <c r="J26" t="n">
         <v>2.26425</v>
       </c>
       <c r="K26" t="n">
-        <v>2.38486210747154</v>
+        <v>2.425911266044917</v>
       </c>
     </row>
     <row r="27">
@@ -3035,13 +3026,13 @@
         <v>2.598</v>
       </c>
       <c r="I27" t="n">
-        <v>2.350909118958581</v>
+        <v>2.21628856712421</v>
       </c>
       <c r="J27" t="n">
         <v>1.5755</v>
       </c>
       <c r="K27" t="n">
-        <v>1.538046333577959</v>
+        <v>1.501643050740533</v>
       </c>
     </row>
     <row r="28">
@@ -3074,13 +3065,13 @@
         <v>1.464</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9341557894611</v>
+        <v>2.046963487917811</v>
       </c>
       <c r="J28" t="n">
         <v>1.202666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.682781915305274</v>
+        <v>1.714867176133942</v>
       </c>
     </row>
     <row r="29">
@@ -3113,13 +3104,13 @@
         <v>1.402</v>
       </c>
       <c r="I29" t="n">
-        <v>1.527779455398029</v>
+        <v>1.589093685298639</v>
       </c>
       <c r="J29" t="n">
         <v>1.1765</v>
       </c>
       <c r="K29" t="n">
-        <v>1.264480872067553</v>
+        <v>1.276782935770268</v>
       </c>
     </row>
     <row r="30">
@@ -3152,13 +3143,13 @@
         <v>2.042</v>
       </c>
       <c r="I30" t="n">
-        <v>1.780429802997515</v>
+        <v>1.773135831510515</v>
       </c>
       <c r="J30" t="n">
         <v>1.508666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.17926914763693</v>
+        <v>1.182983620623201</v>
       </c>
     </row>
     <row r="31">
@@ -3187,13 +3178,13 @@
         <v>7.505999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>7.593274166815225</v>
+        <v>7.625481571851176</v>
       </c>
       <c r="J31" t="n">
         <v>1.8765</v>
       </c>
       <c r="K31" t="n">
-        <v>1.898318541703806</v>
+        <v>1.906370392962794</v>
       </c>
     </row>
     <row r="32">
@@ -3226,13 +3217,13 @@
         <v>2.347</v>
       </c>
       <c r="I32" t="n">
-        <v>1.613707493165421</v>
+        <v>1.665934357401471</v>
       </c>
       <c r="J32" t="n">
         <v>1.196</v>
       </c>
       <c r="K32" t="n">
-        <v>1.210334758106222</v>
+        <v>1.227424225014528</v>
       </c>
     </row>
     <row r="33">
@@ -3265,13 +3256,13 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.490481394676311</v>
+        <v>1.540673138099821</v>
       </c>
       <c r="J33" t="n">
         <v>0.8406666666666668</v>
       </c>
       <c r="K33" t="n">
-        <v>1.069196562412963</v>
+        <v>1.110276895484575</v>
       </c>
     </row>
     <row r="34">
@@ -3304,13 +3295,13 @@
         <v>1.481</v>
       </c>
       <c r="I34" t="n">
-        <v>1.682635643035865</v>
+        <v>1.693364043978105</v>
       </c>
       <c r="J34" t="n">
         <v>0.7117500000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9073546471057639</v>
+        <v>0.8925296023198701</v>
       </c>
     </row>
     <row r="35">
@@ -3343,13 +3334,13 @@
         <v>1.458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.198897805881131</v>
+        <v>1.206153192889763</v>
       </c>
       <c r="J35" t="n">
         <v>0.9506666666666668</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7448227346518818</v>
+        <v>0.7597761877716707</v>
       </c>
     </row>
     <row r="36">
@@ -3378,13 +3369,13 @@
         <v>6.886</v>
       </c>
       <c r="I36" t="n">
-        <v>5.985722336758728</v>
+        <v>6.10612473236916</v>
       </c>
       <c r="J36" t="n">
         <v>1.7215</v>
       </c>
       <c r="K36" t="n">
-        <v>1.496430584189682</v>
+        <v>1.52653118309229</v>
       </c>
     </row>
   </sheetData>
